--- a/msm/demo/msm_report.xlsx
+++ b/msm/demo/msm_report.xlsx
@@ -94,13 +94,13 @@
     <t>Variable</t>
   </si>
   <si>
-    <t>treatment</t>
-  </si>
-  <si>
-    <t>period</t>
-  </si>
-  <si>
-    <t>_msm_period_sq</t>
+    <t>Treatment</t>
+  </si>
+  <si>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Period^2</t>
   </si>
   <si>
     <t>age</t>
@@ -109,7 +109,7 @@
     <t>sex</t>
   </si>
   <si>
-    <t>_cons</t>
+    <t>Constant</t>
   </si>
   <si>
     <t>OR</t>
@@ -179,466 +179,493 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="268">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="274">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1477,7 +1504,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="208">
+  <borders count="214">
     <border>
       <left/>
       <right/>
@@ -2308,6 +2335,48 @@
     <border>
       <left style="none"/>
       <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
       <top style="thin"/>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -2890,7 +2959,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="208">
+  <cellXfs count="214">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -3220,238 +3289,238 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="87" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="88" xfId="0"/>
-    <xf numFmtId="0" fontId="109" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="109" fillId="0" borderId="89" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="110" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="111" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="112" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="113" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="114" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="110" fillId="0" borderId="90" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="111" fillId="0" borderId="91" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="112" fillId="0" borderId="92" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="113" fillId="0" borderId="93" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="114" fillId="0" borderId="94" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="115" fillId="0" borderId="95" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="116" fillId="0" borderId="96" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="118" fillId="0" borderId="97" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="120" fillId="0" borderId="98" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="122" fillId="0" borderId="99" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="124" fillId="0" borderId="100" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="125" fillId="0" borderId="101" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="126" fillId="0" borderId="102" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="127" fillId="0" borderId="103" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="128" fillId="0" borderId="104" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="134" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="129" fillId="0" borderId="105" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="135" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="130" fillId="0" borderId="106" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="136" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="131" fillId="0" borderId="107" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="132" fillId="0" borderId="108" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="133" fillId="0" borderId="109" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="134" fillId="0" borderId="110" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="135" fillId="0" borderId="111" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="141" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="136" fillId="0" borderId="112" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="142" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="138" fillId="0" borderId="113" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="144" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="140" fillId="0" borderId="114" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="146" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="142" fillId="0" borderId="115" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="148" fillId="0" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="144" fillId="0" borderId="116" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="150" fillId="0" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="145" fillId="0" borderId="117" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="151" fillId="0" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="146" fillId="0" borderId="118" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="152" fillId="0" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="147" fillId="0" borderId="119" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="153" fillId="0" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="148" fillId="0" borderId="120" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="154" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="149" fillId="12" borderId="121" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="155" fillId="12" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="150" fillId="13" borderId="122" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="156" fillId="13" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="151" fillId="14" borderId="123" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="157" fillId="14" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="152" fillId="15" borderId="124" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="158" fillId="15" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="153" fillId="16" borderId="125" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="159" fillId="16" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="154" fillId="17" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="160" fillId="17" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="155" fillId="18" borderId="127" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="161" fillId="18" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="156" fillId="19" borderId="128" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="162" fillId="19" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="157" fillId="20" borderId="129" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="163" fillId="20" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="158" fillId="21" borderId="130" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="164" fillId="21" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="159" fillId="22" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="165" fillId="22" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="160" fillId="23" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="166" fillId="23" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="161" fillId="24" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="167" fillId="24" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="162" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="163" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="164" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="165" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="166" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="167" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="168" fillId="25" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="168" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="170" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="171" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="172" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="173" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="174" fillId="25" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="169" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="170" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="171" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="172" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="173" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="174" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="0" fontId="175" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3469,30 +3538,30 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="179" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="180" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="181" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="182" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="182" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="183" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="184" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="185" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="185" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3500,7 +3569,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="187" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="187" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3508,7 +3577,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="189" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="189" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3516,32 +3585,32 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="191" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="191" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="193" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="195" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="197" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="192" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="193" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="194" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="195" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="196" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="197" fillId="26" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="198" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -3564,135 +3633,159 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="203" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="203" fillId="26" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="204" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="205" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="206" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="207" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="208" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="207" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="209" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="211" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="213" fillId="27" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="219" fillId="27" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="215" fillId="28" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="221" fillId="28" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="217" fillId="29" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="223" fillId="29" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="219" fillId="30" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="225" fillId="30" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="221" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="223" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="225" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="227" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="229" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="229" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="231" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="233" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="235" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="237" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="237" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="239" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="241" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="243" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="245" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="247" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="245" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="247" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="249" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="251" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="253" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="253" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="255" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="257" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="259" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="261" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="261" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="263" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="265" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="267" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="269" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3827,115 +3920,115 @@
   </cols>
   <sheetData>
     <row r="1" s="84" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="176" t="s">
+      <c r="A1" s="182" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="177" t="s">
+      <c r="B1" s="183" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="178" t="s">
+      <c r="C1" s="184" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="179" t="s">
+      <c r="D1" s="185" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="180" t="s">
+      <c r="A2" s="186" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="181" t="s">
+      <c r="B2" s="187" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="182" t="s">
+      <c r="C2" s="188" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="183" t="s">
+      <c r="D2" s="189" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="190" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="185">
-        <v>3</v>
-      </c>
-      <c r="C3" s="186">
-        <v>3</v>
-      </c>
-      <c r="D3" s="187">
-        <v>3</v>
+      <c r="B3" s="191">
+        <v>0.7672943522249035</v>
+      </c>
+      <c r="C3" s="192" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="193" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="188" t="s">
+      <c r="A4" s="194" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="189">
-        <v>4</v>
-      </c>
-      <c r="C4" s="190">
-        <v>4</v>
-      </c>
-      <c r="D4" s="191">
-        <v>4</v>
+      <c r="B4" s="195">
+        <v>0.96990480543369195</v>
+      </c>
+      <c r="C4" s="196" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="197" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="192" t="s">
+      <c r="A5" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="193">
-        <v>5</v>
-      </c>
-      <c r="C5" s="194">
-        <v>5</v>
-      </c>
-      <c r="D5" s="195">
-        <v>5</v>
+      <c r="B5" s="199">
+        <v>1.0135738905506451</v>
+      </c>
+      <c r="C5" s="200" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="201" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="196" t="s">
+      <c r="A6" s="202" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="197">
-        <v>6</v>
-      </c>
-      <c r="C6" s="198">
-        <v>6</v>
-      </c>
-      <c r="D6" s="199">
-        <v>6</v>
+      <c r="B6" s="203">
+        <v>1.052812145678234</v>
+      </c>
+      <c r="C6" s="204" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="205" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="200" t="s">
+      <c r="A7" s="206" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="201">
-        <v>7</v>
-      </c>
-      <c r="C7" s="202">
-        <v>7</v>
-      </c>
-      <c r="D7" s="203">
-        <v>7</v>
+      <c r="B7" s="207">
+        <v>0.91156457885765974</v>
+      </c>
+      <c r="C7" s="208" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="209" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="204" t="s">
+      <c r="A8" s="210" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="205">
-        <v>8</v>
-      </c>
-      <c r="C8" s="206">
-        <v>8</v>
-      </c>
-      <c r="D8" s="207">
-        <v>8</v>
+      <c r="B8" s="211">
+        <v>0.00049674249516860002</v>
+      </c>
+      <c r="C8" s="212" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="213" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/msm/demo/msm_report.xlsx
+++ b/msm/demo/msm_report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="68">
   <si>
     <t>MSM Analysis Summary</t>
   </si>
@@ -174,6 +174,51 @@
   <si>
     <t>&lt;0.001</t>
   </si>
+  <si>
+    <t>0.9803</t>
+  </si>
+  <si>
+    <t>0.3758</t>
+  </si>
+  <si>
+    <t>0.3552 - 2.7933</t>
+  </si>
+  <si>
+    <t>3998.5</t>
+  </si>
+  <si>
+    <t>0.7663</t>
+  </si>
+  <si>
+    <t>0.9704</t>
+  </si>
+  <si>
+    <t>1.0135</t>
+  </si>
+  <si>
+    <t>1.0529</t>
+  </si>
+  <si>
+    <t>0.9121</t>
+  </si>
+  <si>
+    <t>(0.3972, 1.4781)</t>
+  </si>
+  <si>
+    <t>(0.6683, 1.4090)</t>
+  </si>
+  <si>
+    <t>(0.9715, 1.0574)</t>
+  </si>
+  <si>
+    <t>(1.0208, 1.0861)</t>
+  </si>
+  <si>
+    <t>(0.4781, 1.7400)</t>
+  </si>
+  <si>
+    <t>(0.0001, 0.0033)</t>
+  </si>
 </sst>
 </file>
 
@@ -182,10 +227,1071 @@
   <numFmts count="1">
     <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="254">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="507">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1249,7 +2355,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="48">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1371,8 +2477,123 @@
         <fgColor rgb="FFDBE5F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="198">
+  <borders count="395">
     <border>
       <left/>
       <right/>
@@ -2711,11 +3932,1342 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="395">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -3478,6 +6030,770 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="253" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="198" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="199" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="200" xfId="0"/>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="275" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="287" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="289" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="291" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="293" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="299" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="301" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="311" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="313" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="315" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="317" fillId="25" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="26" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="319" fillId="27" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="28" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="321" fillId="29" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="30" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="323" fillId="31" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="325" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="327" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="329" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="331" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="333" fillId="0" borderId="253" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="32" borderId="254" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="335" fillId="0" borderId="255" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="256" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="337" fillId="0" borderId="257" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="258" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="339" fillId="0" borderId="259" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="260" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="341" fillId="0" borderId="261" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="262" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="343" fillId="0" borderId="263" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="264" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="345" fillId="0" borderId="265" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="0" borderId="266" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="347" fillId="0" borderId="267" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="268" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="349" fillId="0" borderId="269" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="270" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="351" fillId="0" borderId="271" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="352" fillId="0" borderId="272" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="353" fillId="0" borderId="273" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="274" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="355" fillId="0" borderId="275" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="0" borderId="276" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="277" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="278" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="279" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="280" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="281" xfId="0"/>
+    <xf numFmtId="166" fontId="357" fillId="0" borderId="282" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="358" fillId="0" borderId="283" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="359" fillId="0" borderId="284" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="360" fillId="0" borderId="285" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="361" fillId="0" borderId="286" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="362" fillId="0" borderId="287" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="0" borderId="288" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="0" borderId="289" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="0" borderId="290" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="291" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="292" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="0" borderId="293" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="0" borderId="294" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="0" borderId="295" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="0" borderId="296" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="382" fillId="0" borderId="297" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="0" borderId="298" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="0" borderId="299" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="0" borderId="300" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="390" fillId="0" borderId="301" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="0" borderId="302" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="0" borderId="303" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="0" borderId="304" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="398" fillId="0" borderId="305" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="0" borderId="306" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="0" borderId="307" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="404" fillId="0" borderId="308" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="406" fillId="0" borderId="309" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="408" fillId="0" borderId="310" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="410" fillId="0" borderId="311" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="412" fillId="0" borderId="312" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="414" fillId="0" borderId="313" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="416" fillId="0" borderId="314" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="418" fillId="0" borderId="315" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="420" fillId="0" borderId="316" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="422" fillId="0" borderId="317" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="424" fillId="0" borderId="318" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="426" fillId="0" borderId="319" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="427" fillId="0" borderId="320" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="428" fillId="0" borderId="321" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="429" fillId="0" borderId="322" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="431" fillId="0" borderId="323" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="433" fillId="0" borderId="324" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="435" fillId="0" borderId="325" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="437" fillId="0" borderId="326" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="439" fillId="0" borderId="327" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="440" fillId="0" borderId="328" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="441" fillId="0" borderId="329" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="442" fillId="0" borderId="330" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="443" fillId="0" borderId="331" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="444" fillId="0" borderId="332" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="445" fillId="0" borderId="333" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="446" fillId="0" borderId="334" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="447" fillId="0" borderId="335" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="448" fillId="0" borderId="336" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="449" fillId="0" borderId="337" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="450" fillId="0" borderId="338" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="451" fillId="0" borderId="339" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="452" fillId="33" borderId="340" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="453" fillId="34" borderId="341" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="454" fillId="35" borderId="342" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="455" fillId="36" borderId="343" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="456" fillId="37" borderId="344" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="457" fillId="38" borderId="345" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="458" fillId="39" borderId="346" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="459" fillId="40" borderId="347" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="460" fillId="41" borderId="348" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="461" fillId="42" borderId="349" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="462" fillId="43" borderId="350" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="463" fillId="44" borderId="351" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="464" fillId="45" borderId="352" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="465" fillId="0" borderId="353" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="466" fillId="0" borderId="354" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="467" fillId="0" borderId="355" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="468" fillId="0" borderId="356" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="469" fillId="0" borderId="357" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="470" fillId="0" borderId="358" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="471" fillId="46" borderId="359" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="472" fillId="0" borderId="360" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="473" fillId="0" borderId="361" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="474" fillId="0" borderId="362" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="475" fillId="0" borderId="363" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="476" fillId="0" borderId="364" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="477" fillId="0" borderId="365" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="478" fillId="47" borderId="366" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="479" fillId="0" borderId="367" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="480" fillId="0" borderId="368" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="481" fillId="0" borderId="369" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="482" fillId="0" borderId="370" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="483" fillId="0" borderId="371" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="484" fillId="0" borderId="372" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="485" fillId="0" borderId="373" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="486" fillId="0" borderId="374" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="487" fillId="0" borderId="375" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="488" fillId="0" borderId="376" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="489" fillId="0" borderId="377" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="490" fillId="0" borderId="378" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="491" fillId="0" borderId="379" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="492" fillId="0" borderId="380" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="493" fillId="0" borderId="381" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="494" fillId="0" borderId="382" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="495" fillId="0" borderId="383" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="496" fillId="0" borderId="384" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="497" fillId="0" borderId="385" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="498" fillId="0" borderId="386" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="499" fillId="0" borderId="387" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="500" fillId="0" borderId="388" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="501" fillId="0" borderId="389" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="502" fillId="0" borderId="390" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="503" fillId="0" borderId="391" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="504" fillId="0" borderId="392" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="505" fillId="0" borderId="393" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="506" fillId="0" borderId="394" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3493,104 +6809,104 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="20.7109375" style="3" customWidth="true"/>
+    <col min="1" max="1" width="22.7109375" style="199" customWidth="true"/>
+    <col min="2" max="2" width="20.7109375" style="200" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="31" t="s">
+    <row r="1" s="198" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="228" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="201" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="243" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="254" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="244" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="70">
+      <c r="B3" s="267">
         <v>4586</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="245" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="71">
+      <c r="B4" s="268">
         <v>500</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="246" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="269" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="247" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="73">
+      <c r="B6" s="270">
         <v>47</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="248" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="74">
+      <c r="B7" s="271">
         <v>1681</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="249" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="75">
+      <c r="B8" s="272">
         <v>49</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="53" t="s">
+      <c r="A9" s="250" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="76">
-        <v>0.98470000000000002</v>
+      <c r="B9" s="273">
+        <v>0.98029999999999995</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="251" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="77">
-        <v>0.3765</v>
+      <c r="B10" s="274">
+        <v>0.37580000000000002</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="252" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="78" t="s">
-        <v>22</v>
+      <c r="B11" s="275" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="68" t="s">
+      <c r="A12" s="265" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="79">
-        <v>4001.0999999999999</v>
+      <c r="B12" s="276">
+        <v>3998.5</v>
       </c>
     </row>
   </sheetData>
@@ -3605,121 +6921,121 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="81" customWidth="true"/>
-    <col min="2" max="2" width="14.7109375" style="82" customWidth="true"/>
-    <col min="3" max="3" width="20.7109375" style="83" customWidth="true"/>
-    <col min="4" max="4" width="12.7109375" style="84" customWidth="true"/>
+    <col min="1" max="1" width="22.7109375" style="278" customWidth="true"/>
+    <col min="2" max="2" width="14.7109375" style="279" customWidth="true"/>
+    <col min="3" max="3" width="20.7109375" style="280" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" style="281" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="80" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="126" t="s">
+    <row r="1" s="277" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="323" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="91" t="s">
+      <c r="B1" s="288" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="91" t="s">
+      <c r="C1" s="288" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="91" t="s">
+      <c r="D1" s="288" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="155" t="s">
+      <c r="A2" s="352" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="152" t="s">
+      <c r="B2" s="349" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="153" t="s">
+      <c r="C2" s="350" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="169" t="s">
+      <c r="D2" s="366" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="156" t="s">
+      <c r="A3" s="353" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="180">
-        <v>0.7672943522249035</v>
+      <c r="B3" s="377">
+        <v>0.76626792133636756</v>
       </c>
-      <c r="C3" s="181" t="s">
-        <v>40</v>
+      <c r="C3" s="378" t="s">
+        <v>62</v>
       </c>
-      <c r="D3" s="192" t="s">
+      <c r="D3" s="389" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="157" t="s">
+      <c r="A4" s="354" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="182">
-        <v>0.96990480543369195</v>
+      <c r="B4" s="379">
+        <v>0.97038766823310219</v>
       </c>
-      <c r="C4" s="183" t="s">
-        <v>41</v>
+      <c r="C4" s="380" t="s">
+        <v>63</v>
       </c>
-      <c r="D4" s="193" t="s">
+      <c r="D4" s="390" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="158" t="s">
+      <c r="A5" s="355" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="184">
-        <v>1.0135738905506451</v>
+      <c r="B5" s="381">
+        <v>1.01353939720834</v>
       </c>
-      <c r="C5" s="185" t="s">
-        <v>42</v>
+      <c r="C5" s="382" t="s">
+        <v>64</v>
       </c>
-      <c r="D5" s="194" t="s">
+      <c r="D5" s="391" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="159" t="s">
+      <c r="A6" s="356" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="186">
-        <v>1.052812145678234</v>
+      <c r="B6" s="383">
+        <v>1.052927408786541</v>
       </c>
-      <c r="C6" s="187" t="s">
-        <v>43</v>
+      <c r="C6" s="384" t="s">
+        <v>65</v>
       </c>
-      <c r="D6" s="195" t="s">
+      <c r="D6" s="392" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="160" t="s">
+      <c r="A7" s="357" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="188">
-        <v>0.91156457885765974</v>
+      <c r="B7" s="385">
+        <v>0.91210781960720699</v>
       </c>
-      <c r="C7" s="189" t="s">
-        <v>44</v>
+      <c r="C7" s="386" t="s">
+        <v>66</v>
       </c>
-      <c r="D7" s="196" t="s">
+      <c r="D7" s="393" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="176" t="s">
+      <c r="A8" s="373" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="190">
-        <v>0.00049674249516860002</v>
+      <c r="B8" s="387">
+        <v>0.00049307646708570004</v>
       </c>
-      <c r="C8" s="191" t="s">
-        <v>45</v>
+      <c r="C8" s="388" t="s">
+        <v>67</v>
       </c>
-      <c r="D8" s="197" t="s">
+      <c r="D8" s="394" t="s">
         <v>52</v>
       </c>
     </row>
